--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487824_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487824_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4975</v>
+        <v>6.2295</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7903</v>
+        <v>5.9627</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.2668</v>
       </c>
       <c r="G2" t="n">
         <v>4.4986</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.207</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.199</v>
+        <v>-0.0266</v>
       </c>
       <c r="U2" t="n">
-        <v>1.406</v>
+        <v>0.9656</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9499</v>
+        <v>3.8563</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2395</v>
+        <v>3.1481</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7104</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3251</v>
+        <v>3.7629</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0644</v>
+        <v>2.544</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3896</v>
+        <v>1.2189</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3705</v>
+        <v>4.6082</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6259</v>
+        <v>2.6096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7446</v>
+        <v>1.9986</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0454</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6904</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.645</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2273</v>
+        <v>0.3014</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9689</v>
+        <v>-0.4195</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2584</v>
+        <v>0.721</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0796</v>
+        <v>3.7647</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5591</v>
+        <v>1.3029</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5206</v>
+        <v>2.4618</v>
       </c>
       <c r="G4" t="n">
         <v>4.4141</v>
@@ -766,13 +766,13 @@
         <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3523</v>
+        <v>0.0374</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1866</v>
+        <v>-0.4429</v>
       </c>
       <c r="U4" t="n">
-        <v>0.539</v>
+        <v>0.4802</v>
       </c>
       <c r="V4" t="n">
         <v>0.3538</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3624</v>
+        <v>3.4688</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6542</v>
+        <v>1.8464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7082000000000001</v>
+        <v>1.6224</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7629</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>2.544</v>
+        <v>-1.0644</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2189</v>
+        <v>1.3896</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6082</v>
+        <v>1.3705</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6096</v>
+        <v>0.6259</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9986</v>
+        <v>0.7446</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-1.0454</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-1.6904</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0.645</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1924</v>
+        <v>0.7462</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9134</v>
+        <v>0.5758</v>
       </c>
       <c r="U5" t="n">
-        <v>0.721</v>
+        <v>0.1703</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3829</v>
+        <v>2.4607</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8778</v>
+        <v>1.9849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5051</v>
+        <v>0.4758</v>
       </c>
       <c r="G6" t="n">
         <v>1.601</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4887</v>
+        <v>-0.4109</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.109</v>
+        <v>-0.0019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3797</v>
+        <v>-0.409</v>
       </c>
       <c r="V6" t="n">
         <v>0.23</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7644</v>
+        <v>0.6763</v>
       </c>
       <c r="E7" t="n">
         <v>-1.3563</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1206</v>
+        <v>2.0325</v>
       </c>
       <c r="G7" t="n">
         <v>-0.105</v>
@@ -1000,13 +1000,13 @@
         <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0463</v>
+        <v>-0.1344</v>
       </c>
       <c r="T7" t="n">
         <v>0.0867</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.133</v>
+        <v>-0.2211</v>
       </c>
       <c r="V7" t="n">
         <v>0.7076</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9574</v>
+        <v>-0.3842</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9115</v>
+        <v>-0.6319</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0459</v>
+        <v>0.2477</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9697</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7796</v>
+        <v>-0.2065</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6524</v>
+        <v>-0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1272</v>
+        <v>0.1664</v>
       </c>
       <c r="V9" t="n">
         <v>1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6807</v>
+        <v>-1.3321</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8778</v>
+        <v>-1.7054</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1971</v>
+        <v>0.3733</v>
       </c>
       <c r="G10" t="n">
         <v>0.0531</v>
@@ -1234,13 +1234,13 @@
         <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1174</v>
+        <v>0.466</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3171</v>
+        <v>-0.1447</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4346</v>
+        <v>0.6107</v>
       </c>
       <c r="V10" t="n">
         <v>0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2479</v>
+        <v>-2.2629</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8094</v>
+        <v>-3.0593</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5616</v>
+        <v>0.7964</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2645</v>
@@ -1312,13 +1312,13 @@
         <v>2.7055</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4183</v>
+        <v>-0.4334</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9539</v>
+        <v>-0.2038</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4645</v>
+        <v>-0.2296</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.1669</v>
+        <v>16.4933</v>
       </c>
       <c r="E12" t="n">
-        <v>7.165899999999999</v>
+        <v>7.492100000000001</v>
       </c>
       <c r="F12" t="n">
         <v>9.001100000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>9.123699999999999</v>
+        <v>9.123700000000001</v>
       </c>
       <c r="H12" t="n">
         <v>2.1638</v>
@@ -1390,13 +1390,13 @@
         <v>15.6089</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9787000000000003</v>
+        <v>1.3048</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2758</v>
+        <v>-0.9498</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2546</v>
+        <v>2.2545</v>
       </c>
       <c r="V12" t="n">
         <v>5.024000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1752</v>
+        <v>2.9148</v>
       </c>
       <c r="E13" t="n">
-        <v>5.688</v>
+        <v>2.7269</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5127</v>
+        <v>0.188</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5052</v>
+        <v>1.1204</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8146</v>
+        <v>2.4177</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3094</v>
+        <v>-1.2973</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7101</v>
+        <v>3.3579</v>
       </c>
       <c r="K13" t="n">
-        <v>3.848</v>
+        <v>3.5897</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8621</v>
+        <v>-0.2319</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.205</v>
+        <v>-2.2374</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0334</v>
+        <v>-1.172</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1716</v>
+        <v>-1.0654</v>
       </c>
       <c r="P13" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5889</v>
+        <v>-0.2649</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0184</v>
+        <v>-0.631</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5705</v>
+        <v>0.3661</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2727</v>
+        <v>2.7791</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8696</v>
+        <v>3.652</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5969</v>
+        <v>-0.8729</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1204</v>
+        <v>1.5052</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4177</v>
+        <v>1.8146</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2973</v>
+        <v>-0.3094</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3579</v>
+        <v>4.7101</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5897</v>
+        <v>3.848</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2319</v>
+        <v>0.8621</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2374</v>
+        <v>-3.205</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.172</v>
+        <v>-2.0334</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0654</v>
+        <v>-1.1716</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.907</v>
+        <v>1.1928</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4882</v>
+        <v>-0.0175</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4188</v>
+        <v>1.2103</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5693</v>
+        <v>0.3844</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6907</v>
+        <v>0.4764</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1214</v>
+        <v>-0.092</v>
       </c>
       <c r="G15" t="n">
         <v>0.4996</v>
@@ -1624,13 +1624,13 @@
         <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1748</v>
+        <v>-0.0101</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4005</v>
+        <v>0.1862</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2257</v>
+        <v>-0.1964</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9376</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4542</v>
+        <v>-0.4144</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5425</v>
+        <v>0.737</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9968</v>
+        <v>-1.1514</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2744</v>
+        <v>-0.0776</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0254</v>
+        <v>-0.0106</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.249</v>
+        <v>-0.0669</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.6532</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3512</v>
+        <v>-0.7308</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1022</v>
+        <v>-0.6247</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.249</v>
+        <v>-0.1061</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3634</v>
+        <v>0.0388</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4658</v>
+        <v>0.0838</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1024</v>
+        <v>-0.045</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6874</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.2211</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2102</v>
+        <v>-0.9968</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0776</v>
+        <v>-0.2744</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0106</v>
+        <v>-0.0254</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0669</v>
+        <v>-0.249</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6532</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.614</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7308</v>
+        <v>-0.3512</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6247</v>
+        <v>-0.1022</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1061</v>
+        <v>-0.249</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2342</v>
+        <v>0.0419</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1305</v>
+        <v>0.1443</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1037</v>
+        <v>-0.1024</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7722</v>
+        <v>-1.1268</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1713</v>
+        <v>-2.6355</v>
       </c>
       <c r="F19" t="n">
-        <v>1.399</v>
+        <v>1.5086</v>
       </c>
       <c r="G19" t="n">
         <v>0.2584</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3875</v>
+        <v>0.2579</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5748</v>
+        <v>-0.039</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1873</v>
+        <v>0.2969</v>
       </c>
       <c r="V19" t="n">
         <v>0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9407</v>
+        <v>-1.8145</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.3527</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3737</v>
+        <v>-1.4618</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0001</v>
@@ -2014,13 +2014,13 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0594</v>
+        <v>0.1856</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1491</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1246</v>
+        <v>0.0365</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1675</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.024</v>
+        <v>-3.788</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8311</v>
+        <v>-2.8789</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1929</v>
+        <v>-0.9091</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2785</v>
+        <v>-0.4084</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7338</v>
+        <v>-1.8379</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5447</v>
+        <v>1.4295</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2371</v>
+        <v>3.0498</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7578</v>
+        <v>0.3425</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4792</v>
+        <v>2.7072</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0414</v>
+        <v>-3.4581</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.976</v>
+        <v>-2.1804</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0654</v>
+        <v>-1.2777</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2081</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8731</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0463</v>
+        <v>-0.466</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5129</v>
+        <v>-0.7257</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5592</v>
+        <v>0.2597</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2349</v>
+        <v>-4.9438</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.629</v>
+        <v>-4.8311</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6059</v>
+        <v>-0.1127</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4084</v>
+        <v>-4.2785</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8379</v>
+        <v>-2.7338</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4295</v>
+        <v>-1.5447</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0498</v>
+        <v>-2.2371</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3425</v>
+        <v>-1.7578</v>
       </c>
       <c r="L22" t="n">
-        <v>2.7072</v>
+        <v>-0.4792</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4581</v>
+        <v>-2.0414</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1804</v>
+        <v>-0.976</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2777</v>
+        <v>-1.0654</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9137</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2893</v>
+        <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9129</v>
+        <v>0.1266</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4758</v>
+        <v>-0.5129</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4371</v>
+        <v>0.6394</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2384</v>
+        <v>-7.121</v>
       </c>
       <c r="E23" t="n">
         <v>-5.0758</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1626</v>
+        <v>-2.0452</v>
       </c>
       <c r="G23" t="n">
         <v>-7.4685</v>
@@ -2248,13 +2248,13 @@
         <v>2.4974</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7699</v>
+        <v>-0.6524</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8919</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1221</v>
+        <v>0.2395</v>
       </c>
       <c r="V23" t="n">
         <v>0.5838</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.1671</v>
+        <v>-14.7384</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.001299999999999</v>
+        <v>-9.001200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.166</v>
+        <v>-5.7372</v>
       </c>
       <c r="G24" t="n">
         <v>-9.123899999999999</v>
@@ -2302,7 +2302,7 @@
         <v>7.942399999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>8.513999999999999</v>
+        <v>8.514000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-0.5716000000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-6.3884</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.040700000000001</v>
+        <v>-1.0407</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.6089</v>
@@ -2326,16 +2326,16 @@
         <v>14.5683</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9786999999999997</v>
+        <v>0.4502000000000003</v>
       </c>
       <c r="T24" t="n">
         <v>-2.2546</v>
       </c>
       <c r="U24" t="n">
-        <v>1.276</v>
+        <v>2.7046</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.0239</v>
+        <v>-5.023899999999999</v>
       </c>
       <c r="W24" t="n">
         <v>0.9198999999999999</v>
